--- a/downloads/CardShow_Inventory_Template.xlsx
+++ b/downloads/CardShow_Inventory_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stephenwilhelm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94EBACED-C281-AC44-82F9-71E569B3DD99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60B49EE-2647-E64A-9009-9DFA3C5147A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="27640" windowHeight="15760" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Column Guide" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Inventory!$A$3:$P$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Inventory!$A$1:$P$17</definedName>
   </definedNames>
   <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
@@ -29,13 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="151">
-  <si>
-    <t>CardShow  —  Seller Inventory Template</t>
-  </si>
-  <si>
-    <t>Upload at getcardshow.com  ·  Headers auto-detect — do not rename them  ·  Required: Card Title  ·  All other fields optional</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="149">
   <si>
     <t>Card Title</t>
   </si>
@@ -1069,7 +1063,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W701"/>
+  <dimension ref="A1:W699"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34" style="35" customWidth="1"/>
@@ -1089,663 +1083,673 @@
     <col min="16" max="16" width="24" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-    </row>
-    <row r="2" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-    </row>
-    <row r="3" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="6" t="s">
+    </row>
+    <row r="2" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
+      <c r="C2" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="E2" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="F2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="G2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="H2" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="I2" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="J2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="K2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="L2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="M2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="N2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="O2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="P2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="O4" s="7" t="s">
+    </row>
+    <row r="3" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="B3" s="20" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C3" s="21">
+        <v>2024</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="23">
+        <v>10</v>
+      </c>
+      <c r="H3" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="22">
+        <v>100039513</v>
+      </c>
+      <c r="J3" s="24"/>
+      <c r="K3" s="25">
+        <v>148</v>
+      </c>
+      <c r="L3" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+    </row>
+    <row r="4" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="27">
+        <v>2023</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="28">
+        <v>1</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="29">
+        <v>9.5</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" s="28">
+        <v>55443322</v>
+      </c>
+      <c r="J4" s="30"/>
+      <c r="K4" s="31">
+        <v>320</v>
+      </c>
+      <c r="L4" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="M4" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="N4" s="30"/>
+      <c r="O4" s="30"/>
+      <c r="P4" s="30"/>
+    </row>
+    <row r="5" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C5" s="21">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>37</v>
+        <v>47</v>
+      </c>
+      <c r="E5" s="22">
+        <v>249</v>
       </c>
       <c r="F5" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="K5" s="25">
+        <v>45</v>
+      </c>
+      <c r="L5" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="23">
-        <v>10</v>
-      </c>
-      <c r="H5" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="I5" s="22">
-        <v>100039513</v>
-      </c>
-      <c r="J5" s="24"/>
-      <c r="K5" s="25">
-        <v>148</v>
-      </c>
-      <c r="L5" s="20" t="s">
-        <v>40</v>
-      </c>
       <c r="M5" s="20" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="N5" s="24"/>
       <c r="O5" s="24"/>
       <c r="P5" s="24"/>
     </row>
-    <row r="6" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="19" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C6" s="27">
-        <v>2023</v>
+        <v>1986</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="E6" s="28">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G6" s="29">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="I6" s="28">
-        <v>55443322</v>
+        <v>77665544</v>
       </c>
       <c r="J6" s="30"/>
       <c r="K6" s="31">
-        <v>320</v>
+        <v>18500</v>
       </c>
       <c r="L6" s="26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M6" s="26" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="N6" s="30"/>
       <c r="O6" s="30"/>
       <c r="P6" s="30"/>
     </row>
-    <row r="7" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="21">
+        <v>2024</v>
+      </c>
+      <c r="D7" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="21">
-        <v>2019</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>49</v>
-      </c>
       <c r="E7" s="22">
-        <v>249</v>
+        <v>1</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="20" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="G7" s="23">
+        <v>9</v>
+      </c>
+      <c r="H7" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="22">
+        <v>22334455</v>
+      </c>
+      <c r="J7" s="24"/>
       <c r="K7" s="25">
-        <v>45</v>
+        <v>1800</v>
       </c>
       <c r="L7" s="20" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M7" s="20" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="N7" s="24"/>
       <c r="O7" s="24"/>
       <c r="P7" s="24"/>
     </row>
-    <row r="8" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="19" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C8" s="27">
-        <v>1986</v>
+        <v>2023</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="E8" s="28">
-        <v>57</v>
+        <v>62</v>
+      </c>
+      <c r="E8" s="28" t="s">
+        <v>63</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="G8" s="29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H8" s="26" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I8" s="28">
-        <v>77665544</v>
+        <v>33221144</v>
       </c>
       <c r="J8" s="30"/>
       <c r="K8" s="31">
-        <v>18500</v>
+        <v>580</v>
       </c>
       <c r="L8" s="26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M8" s="26" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="N8" s="30"/>
       <c r="O8" s="30"/>
       <c r="P8" s="30"/>
     </row>
-    <row r="9" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="19" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C9" s="21">
-        <v>2024</v>
+        <v>1999</v>
       </c>
       <c r="D9" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="22">
-        <v>1</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="G9" s="23">
-        <v>9</v>
-      </c>
-      <c r="H9" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="I9" s="22">
-        <v>22334455</v>
-      </c>
-      <c r="J9" s="24"/>
       <c r="K9" s="25">
-        <v>1800</v>
+        <v>4800</v>
       </c>
       <c r="L9" s="20" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M9" s="20" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="N9" s="24"/>
       <c r="O9" s="24"/>
       <c r="P9" s="24"/>
     </row>
-    <row r="10" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="19" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C10" s="27">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G10" s="29">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="H10" s="26" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="I10" s="28">
-        <v>33221144</v>
+        <v>44556677</v>
       </c>
       <c r="J10" s="30"/>
       <c r="K10" s="31">
-        <v>580</v>
+        <v>1200</v>
       </c>
       <c r="L10" s="26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M10" s="26" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N10" s="30"/>
       <c r="O10" s="30"/>
       <c r="P10" s="30"/>
     </row>
-    <row r="11" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="19" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="C11" s="21">
-        <v>1999</v>
+        <v>2022</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G11" s="24"/>
       <c r="H11" s="24"/>
       <c r="I11" s="24"/>
       <c r="J11" s="20" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="K11" s="25">
-        <v>4800</v>
+        <v>185</v>
       </c>
       <c r="L11" s="20" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M11" s="20" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="N11" s="24"/>
       <c r="O11" s="24"/>
       <c r="P11" s="24"/>
     </row>
-    <row r="12" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>74</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="B12" s="30"/>
       <c r="C12" s="27">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="E12" s="28" t="s">
-        <v>76</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="E12" s="32"/>
       <c r="F12" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="G12" s="29">
-        <v>9.5</v>
-      </c>
-      <c r="H12" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="I12" s="28">
-        <v>44556677</v>
-      </c>
-      <c r="J12" s="30"/>
+        <v>85</v>
+      </c>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="26" t="s">
+        <v>86</v>
+      </c>
       <c r="K12" s="31">
-        <v>1200</v>
+        <v>145</v>
       </c>
       <c r="L12" s="26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M12" s="26" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="N12" s="30"/>
       <c r="O12" s="30"/>
       <c r="P12" s="30"/>
     </row>
-    <row r="13" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="19" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C13" s="21">
         <v>2022</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>82</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="E13" s="33"/>
       <c r="F13" s="20" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="G13" s="24"/>
       <c r="H13" s="24"/>
       <c r="I13" s="24"/>
       <c r="J13" s="20" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="K13" s="25">
-        <v>185</v>
+        <v>120</v>
       </c>
       <c r="L13" s="20" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M13" s="20" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="N13" s="24"/>
       <c r="O13" s="24"/>
       <c r="P13" s="24"/>
     </row>
-    <row r="14" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="B14" s="30"/>
+        <v>92</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>93</v>
+      </c>
       <c r="C14" s="27">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D14" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="E14" s="32"/>
+        <v>42</v>
+      </c>
+      <c r="E14" s="28" t="s">
+        <v>94</v>
+      </c>
       <c r="F14" s="26" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="G14" s="30"/>
       <c r="H14" s="30"/>
       <c r="I14" s="30"/>
       <c r="J14" s="26" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="K14" s="31">
-        <v>145</v>
+        <v>890</v>
       </c>
       <c r="L14" s="26" t="s">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="M14" s="26" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="N14" s="30"/>
       <c r="O14" s="30"/>
       <c r="P14" s="30"/>
     </row>
-    <row r="15" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="19" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="C15" s="21">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="E15" s="33"/>
+        <v>99</v>
+      </c>
+      <c r="E15" s="22">
+        <v>50</v>
+      </c>
       <c r="F15" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="20" t="s">
-        <v>51</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="G15" s="23">
+        <v>10</v>
+      </c>
+      <c r="H15" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="I15" s="22">
+        <v>12345678</v>
+      </c>
+      <c r="J15" s="24"/>
       <c r="K15" s="25">
-        <v>120</v>
+        <v>75000</v>
       </c>
       <c r="L15" s="20" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="M15" s="20" t="s">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="N15" s="24"/>
       <c r="O15" s="24"/>
       <c r="P15" s="24"/>
     </row>
-    <row r="16" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="B16" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="C16" s="27">
-        <v>2025</v>
-      </c>
-      <c r="D16" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="F16" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="K16" s="31">
-        <v>890</v>
-      </c>
-      <c r="L16" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="M16" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="N16" s="30"/>
-      <c r="O16" s="30"/>
-      <c r="P16" s="30"/>
+    <row r="16" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="16"/>
+      <c r="R16" s="16"/>
+      <c r="S16" s="16"/>
+      <c r="T16" s="16"/>
+      <c r="U16" s="16"/>
+      <c r="V16" s="16"/>
+      <c r="W16" s="16"/>
     </row>
     <row r="17" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="C17" s="21">
-        <v>2024</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="E17" s="22">
-        <v>50</v>
-      </c>
-      <c r="F17" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="G17" s="23">
-        <v>10</v>
-      </c>
-      <c r="H17" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="I17" s="22">
-        <v>12345678</v>
-      </c>
-      <c r="J17" s="24"/>
-      <c r="K17" s="25">
-        <v>75000</v>
-      </c>
-      <c r="L17" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="M17" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="N17" s="24"/>
-      <c r="O17" s="24"/>
-      <c r="P17" s="24"/>
-    </row>
-    <row r="18" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="16"/>
+      <c r="R17" s="16"/>
+      <c r="S17" s="16"/>
+      <c r="T17" s="16"/>
+      <c r="U17" s="16"/>
+      <c r="V17" s="16"/>
+      <c r="W17" s="16"/>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A18" s="13"/>
       <c r="B18" s="13"/>
       <c r="C18" s="14"/>
@@ -1770,7 +1774,7 @@
       <c r="V18" s="16"/>
       <c r="W18" s="16"/>
     </row>
-    <row r="19" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19" s="17"/>
       <c r="B19" s="17"/>
       <c r="C19" s="18"/>
@@ -5546,22 +5550,22 @@
       <c r="W169" s="16"/>
     </row>
     <row r="170" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A170" s="13"/>
-      <c r="B170" s="13"/>
-      <c r="C170" s="14"/>
-      <c r="D170" s="13"/>
-      <c r="E170" s="15"/>
-      <c r="F170" s="13"/>
-      <c r="G170" s="13"/>
-      <c r="H170" s="13"/>
-      <c r="I170" s="13"/>
-      <c r="J170" s="13"/>
-      <c r="K170" s="13"/>
-      <c r="L170" s="13"/>
-      <c r="M170" s="13"/>
-      <c r="N170" s="13"/>
-      <c r="O170" s="13"/>
-      <c r="P170" s="13"/>
+      <c r="A170" s="34"/>
+      <c r="B170" s="34"/>
+      <c r="C170" s="34"/>
+      <c r="D170" s="34"/>
+      <c r="E170" s="34"/>
+      <c r="F170" s="34"/>
+      <c r="G170" s="34"/>
+      <c r="H170" s="34"/>
+      <c r="I170" s="34"/>
+      <c r="J170" s="34"/>
+      <c r="K170" s="34"/>
+      <c r="L170" s="34"/>
+      <c r="M170" s="34"/>
+      <c r="N170" s="34"/>
+      <c r="O170" s="34"/>
+      <c r="P170" s="34"/>
       <c r="Q170" s="16"/>
       <c r="R170" s="16"/>
       <c r="S170" s="16"/>
@@ -5571,22 +5575,22 @@
       <c r="W170" s="16"/>
     </row>
     <row r="171" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A171" s="17"/>
-      <c r="B171" s="17"/>
-      <c r="C171" s="18"/>
-      <c r="D171" s="17"/>
-      <c r="E171" s="17"/>
-      <c r="F171" s="17"/>
-      <c r="G171" s="17"/>
-      <c r="H171" s="17"/>
-      <c r="I171" s="17"/>
-      <c r="J171" s="17"/>
-      <c r="K171" s="17"/>
-      <c r="L171" s="17"/>
-      <c r="M171" s="17"/>
-      <c r="N171" s="17"/>
-      <c r="O171" s="17"/>
-      <c r="P171" s="17"/>
+      <c r="A171" s="34"/>
+      <c r="B171" s="34"/>
+      <c r="C171" s="34"/>
+      <c r="D171" s="34"/>
+      <c r="E171" s="34"/>
+      <c r="F171" s="34"/>
+      <c r="G171" s="34"/>
+      <c r="H171" s="34"/>
+      <c r="I171" s="34"/>
+      <c r="J171" s="34"/>
+      <c r="K171" s="34"/>
+      <c r="L171" s="34"/>
+      <c r="M171" s="34"/>
+      <c r="N171" s="34"/>
+      <c r="O171" s="34"/>
+      <c r="P171" s="34"/>
       <c r="Q171" s="16"/>
       <c r="R171" s="16"/>
       <c r="S171" s="16"/>
@@ -18795,71 +18799,17 @@
       <c r="V699" s="16"/>
       <c r="W699" s="16"/>
     </row>
-    <row r="700" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A700" s="34"/>
-      <c r="B700" s="34"/>
-      <c r="C700" s="34"/>
-      <c r="D700" s="34"/>
-      <c r="E700" s="34"/>
-      <c r="F700" s="34"/>
-      <c r="G700" s="34"/>
-      <c r="H700" s="34"/>
-      <c r="I700" s="34"/>
-      <c r="J700" s="34"/>
-      <c r="K700" s="34"/>
-      <c r="L700" s="34"/>
-      <c r="M700" s="34"/>
-      <c r="N700" s="34"/>
-      <c r="O700" s="34"/>
-      <c r="P700" s="34"/>
-      <c r="Q700" s="16"/>
-      <c r="R700" s="16"/>
-      <c r="S700" s="16"/>
-      <c r="T700" s="16"/>
-      <c r="U700" s="16"/>
-      <c r="V700" s="16"/>
-      <c r="W700" s="16"/>
-    </row>
-    <row r="701" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A701" s="34"/>
-      <c r="B701" s="34"/>
-      <c r="C701" s="34"/>
-      <c r="D701" s="34"/>
-      <c r="E701" s="34"/>
-      <c r="F701" s="34"/>
-      <c r="G701" s="34"/>
-      <c r="H701" s="34"/>
-      <c r="I701" s="34"/>
-      <c r="J701" s="34"/>
-      <c r="K701" s="34"/>
-      <c r="L701" s="34"/>
-      <c r="M701" s="34"/>
-      <c r="N701" s="34"/>
-      <c r="O701" s="34"/>
-      <c r="P701" s="34"/>
-      <c r="Q701" s="16"/>
-      <c r="R701" s="16"/>
-      <c r="S701" s="16"/>
-      <c r="T701" s="16"/>
-      <c r="U701" s="16"/>
-      <c r="V701" s="16"/>
-      <c r="W701" s="16"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:P19" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <mergeCells count="2">
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A2:P2"/>
-  </mergeCells>
+  <autoFilter ref="A1:P17" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="L5:L1019" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="L3:L1017" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Available,Sold,On Hold"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H5:H1019" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H3:H1017" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"PSA,BGS,CGC,SGC,TAG,Arena Club"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J5:J1019" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J3:J1017" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Near Mint,Lightly Played,Moderately Played,Heavily Played,Damaged,Factory Sealed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -18883,7 +18833,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -18892,7 +18842,7 @@
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -18901,296 +18851,296 @@
     </row>
     <row r="3" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>109</v>
-      </c>
       <c r="E3" s="6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B4" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="E4" s="8" t="s">
         <v>111</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" s="11" t="s">
         <v>114</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -19199,7 +19149,7 @@
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -19208,7 +19158,7 @@
     </row>
     <row r="23" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -19217,7 +19167,7 @@
     </row>
     <row r="24" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -19226,7 +19176,7 @@
     </row>
     <row r="25" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -19235,7 +19185,7 @@
     </row>
     <row r="26" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -19244,7 +19194,7 @@
     </row>
     <row r="27" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
